--- a/data/trans_dic/P32E$casa_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 64,35</t>
+          <t>5,82; 61,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,67; 51,53</t>
+          <t>13,78; 51,46</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 54,84</t>
+          <t>9,27; 56,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 57,85</t>
+          <t>1,23; 66,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 43,05</t>
+          <t>9,52; 45,73</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,35; 73,37</t>
+          <t>34,31; 75,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,44; 85,19</t>
+          <t>15,61; 86,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,83; 71,0</t>
+          <t>35,82; 70,47</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,5; 75,7</t>
+          <t>38,98; 76,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 50,13</t>
+          <t>4,07; 45,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,72; 62,93</t>
+          <t>31,62; 63,7</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,37; 87,05</t>
+          <t>51,98; 86,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,97; 89,99</t>
+          <t>30,02; 86,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,26; 82,97</t>
+          <t>54,94; 82,23</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52,19; 90,94</t>
+          <t>50,78; 91,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,39; 87,75</t>
+          <t>15,56; 88,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,17; 85,65</t>
+          <t>52,45; 86,16</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,51; 100,0</t>
+          <t>22,48; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,02; 92,3</t>
+          <t>27,27; 91,55</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,15; 60,5</t>
+          <t>43,35; 61,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,41; 47,6</t>
+          <t>22,22; 47,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,39; 54,11</t>
+          <t>40,02; 55,19</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>991; 9879</t>
+          <t>893; 9456</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5605; 21123</t>
+          <t>5651; 21097</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1731; 12593</t>
+          <t>2128; 12935</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>354; 7833</t>
+          <t>166; 8971</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3901; 15715</t>
+          <t>3475; 16692</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9493; 19705</t>
+          <t>9213; 20200</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>842; 4645</t>
+          <t>851; 4722</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11899; 22939</t>
+          <t>11572; 22767</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10623; 20885</t>
+          <t>10753; 21174</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423; 4531</t>
+          <t>368; 4133</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11984; 23050</t>
+          <t>11580; 23332</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12124; 19774</t>
+          <t>11809; 19537</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1650; 5505</t>
+          <t>1836; 5308</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15645; 23923</t>
+          <t>15843; 23711</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6914; 12048</t>
+          <t>6728; 12137</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>501; 3052</t>
+          <t>541; 3069</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8058; 14327</t>
+          <t>8773; 14412</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1197; 5090</t>
+          <t>1144; 5090</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1981; 6302</t>
+          <t>1862; 6251</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>62190; 87186</t>
+          <t>62476; 87956</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11715; 26045</t>
+          <t>12155; 25764</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>78322; 107576</t>
+          <t>79562; 109730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$casa_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 62,81</t>
+          <t>18,52; 72,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 61,59</t>
+          <t>5,89; 57,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,78; 51,46</t>
+          <t>18,82; 57,6</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 56,33</t>
+          <t>10,44; 56,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 66,26</t>
+          <t>6,28; 62,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 45,73</t>
+          <t>12,33; 45,3</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,31; 75,21</t>
+          <t>38,01; 76,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 86,6</t>
+          <t>21,2; 86,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,82; 70,47</t>
+          <t>42,06; 76,07</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,98; 76,75</t>
+          <t>38,02; 73,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 45,73</t>
+          <t>6,67; 50,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,62; 63,7</t>
+          <t>34,09; 63,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,98; 86,0</t>
+          <t>52,2; 85,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,02; 86,77</t>
+          <t>25,58; 89,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,94; 82,23</t>
+          <t>52,1; 81,36</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50,78; 91,61</t>
+          <t>49,83; 90,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,56; 88,23</t>
+          <t>16,54; 88,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,45; 86,16</t>
+          <t>47,94; 85,95</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,48; 100,0</t>
+          <t>20,05; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,27; 91,55</t>
+          <t>28,54; 93,17</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,35; 61,03</t>
+          <t>44,88; 62,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,22; 47,09</t>
+          <t>24,41; 49,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40,02; 55,19</t>
+          <t>41,18; 56,08</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>17077</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3239; 16107</t>
+          <t>5472; 21407</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>893; 9456</t>
+          <t>1057; 10256</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5651; 21097</t>
+          <t>8942; 27367</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>11975</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2128; 12935</t>
+          <t>2917; 15717</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>166; 8971</t>
+          <t>1004; 9910</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3475; 16692</t>
+          <t>5410; 19887</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>21313</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9213; 20200</t>
+          <t>11283; 22703</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>851; 4722</t>
+          <t>1397; 5692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11572; 22767</t>
+          <t>15258; 27593</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>17333</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>19915</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10753; 21174</t>
+          <t>11585; 22415</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>368; 4133</t>
+          <t>717; 5370</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11580; 23332</t>
+          <t>14046; 26017</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>20767</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11809; 19537</t>
+          <t>12131; 19984</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1836; 5308</t>
+          <t>1717; 5996</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15843; 23711</t>
+          <t>15603; 24367</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>12822</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6728; 12137</t>
+          <t>7210; 13154</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>541; 3069</t>
+          <t>636; 3407</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8773; 14412</t>
+          <t>8782; 15745</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5920</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1144; 5090</t>
+          <t>1232; 6143</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1738</t>
+          <t>0; 2368</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1862; 6251</t>
+          <t>2429; 7929</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>87085</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>109790</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>62476; 87956</t>
+          <t>72468; 100652</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12155; 25764</t>
+          <t>15670; 31963</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>79562; 109730</t>
+          <t>92920; 126553</t>
         </is>
       </c>
     </row>
